--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110333</v>
+        <v>110339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110339</v>
+        <v>110341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110341</v>
+        <v>110342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110342</v>
+        <v>110348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110348</v>
+        <v>110352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110352</v>
+        <v>110354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110354</v>
+        <v>110356</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110356</v>
+        <v>110369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110369</v>
+        <v>110371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110371</v>
+        <v>110376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110376</v>
+        <v>110398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110398</v>
+        <v>110399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110399</v>
+        <v>110404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110404</v>
+        <v>110407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110407</v>
+        <v>110413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110413</v>
+        <v>110414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110414</v>
+        <v>110426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110426</v>
+        <v>110427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110427</v>
+        <v>110430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110430</v>
+        <v>110432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 16113-2026 artfynd.xlsx
+++ b/artfynd/A 16113-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932700</v>
       </c>
       <c r="B2" t="n">
-        <v>110432</v>
+        <v>110436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136932702</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>136932705</v>
       </c>
       <c r="B4" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
